--- a/data/trans_orig/P11_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P11_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2007</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>132259</t>
+          <t>133761</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>174879</t>
+          <t>175728</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>178648</t>
+          <t>183979</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>226416</t>
+          <t>230559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>328974</t>
+          <t>327909</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>391794</t>
+          <t>389946</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>519133</t>
+          <t>518284</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>561753</t>
+          <t>560251</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>461935</t>
+          <t>457792</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>509703</t>
+          <t>504372</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>990569</t>
+          <t>992417</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1053389</t>
+          <t>1054454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>76,28%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128280</t>
+          <t>129338</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>173229</t>
+          <t>174227</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>232085</t>
+          <t>231559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>288955</t>
+          <t>289166</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>372743</t>
+          <t>372426</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>446820</t>
+          <t>442801</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>788571</t>
+          <t>787573</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>833520</t>
+          <t>832462</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>679438</t>
+          <t>679227</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>736308</t>
+          <t>736834</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1483373</t>
+          <t>1487392</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1557450</t>
+          <t>1557767</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110889</t>
+          <t>111039</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154007</t>
+          <t>155780</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>216379</t>
+          <t>215567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>268190</t>
+          <t>266031</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>339177</t>
+          <t>337671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>404517</t>
+          <t>403928</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>524502</t>
+          <t>522729</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>567620</t>
+          <t>567470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>415651</t>
+          <t>417810</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>467462</t>
+          <t>468274</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>957833</t>
+          <t>958422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1023173</t>
+          <t>1024679</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139988</t>
+          <t>139991</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185669</t>
+          <t>183880</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>255851</t>
+          <t>255020</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>311568</t>
+          <t>315188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>404545</t>
+          <t>409749</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>480945</t>
+          <t>483545</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>756553</t>
+          <t>758342</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>802234</t>
+          <t>802231</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>727044</t>
+          <t>723424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>782761</t>
+          <t>783592</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1499889</t>
+          <t>1497289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1576289</t>
+          <t>1571085</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,31%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>552983</t>
+          <t>554337</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>642865</t>
+          <t>643076</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>931344</t>
+          <t>933971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1036340</t>
+          <t>1042379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,67%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1514374</t>
+          <t>1510899</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1655188</t>
+          <t>1649700</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2633678</t>
+          <t>2633467</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2723560</t>
+          <t>2722206</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2342857</t>
+          <t>2336818</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2447853</t>
+          <t>2445226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,33%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5000553</t>
+          <t>5006041</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5141367</t>
+          <t>5144842</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2012</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2012 (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>111763</t>
+          <t>112136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154888</t>
+          <t>154348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>210833</t>
+          <t>210018</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>263570</t>
+          <t>265428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>332716</t>
+          <t>336984</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>406746</t>
+          <t>403605</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,2%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>542928</t>
+          <t>543468</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>586053</t>
+          <t>585680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>431606</t>
+          <t>429748</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>484343</t>
+          <t>485158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>986246</t>
+          <t>989387</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1060276</t>
+          <t>1056008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,81%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183928</t>
+          <t>182833</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>238594</t>
+          <t>236595</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>294854</t>
+          <t>293664</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>356242</t>
+          <t>355200</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>491769</t>
+          <t>496973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>574558</t>
+          <t>576251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,2%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>774946</t>
+          <t>776945</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>829612</t>
+          <t>830707</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>673951</t>
+          <t>674993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>735339</t>
+          <t>736529</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,38%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1469175</t>
+          <t>1467482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1551964</t>
+          <t>1546760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,68%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82139</t>
+          <t>82894</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>121148</t>
+          <t>122682</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>194645</t>
+          <t>195050</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>249864</t>
+          <t>246672</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>287161</t>
+          <t>288273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>354775</t>
+          <t>355284</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>633365</t>
+          <t>631831</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>672374</t>
+          <t>671619</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>527310</t>
+          <t>530502</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582529</t>
+          <t>582124</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,85%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1176912</t>
+          <t>1176403</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1244526</t>
+          <t>1243414</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,18%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172717</t>
+          <t>175568</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>226273</t>
+          <t>226891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>299885</t>
+          <t>305167</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>364207</t>
+          <t>364037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>492796</t>
+          <t>494311</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>574241</t>
+          <t>577310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>717545</t>
+          <t>716927</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>771101</t>
+          <t>768250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>687694</t>
+          <t>687864</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>752016</t>
+          <t>746734</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1421478</t>
+          <t>1418409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1502923</t>
+          <t>1501408</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>75,23%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>596618</t>
+          <t>597889</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>691523</t>
+          <t>692568</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1056150</t>
+          <t>1059235</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1177238</t>
+          <t>1173836</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1684174</t>
+          <t>1681452</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1834398</t>
+          <t>1828983</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,26%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2718164</t>
+          <t>2717119</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2813069</t>
+          <t>2811798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2377206</t>
+          <t>2380608</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2498294</t>
+          <t>2495209</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5129733</t>
+          <t>5135148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5279957</t>
+          <t>5282679</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>75,86%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2016</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2016 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118096</t>
+          <t>116144</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>157252</t>
+          <t>158020</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>189484</t>
+          <t>190700</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>241914</t>
+          <t>241294</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>324085</t>
+          <t>322654</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>387913</t>
+          <t>389120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>511797</t>
+          <t>511029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>550953</t>
+          <t>552905</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424146</t>
+          <t>424766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>476576</t>
+          <t>475360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>947196</t>
+          <t>945989</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1011024</t>
+          <t>1012455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,83%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>163537</t>
+          <t>168183</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>215222</t>
+          <t>215856</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>283918</t>
+          <t>285019</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>346725</t>
+          <t>347313</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>461731</t>
+          <t>461602</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>545148</t>
+          <t>543911</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>800743</t>
+          <t>800109</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>852428</t>
+          <t>847782</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>693115</t>
+          <t>692527</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>755922</t>
+          <t>754821</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1510657</t>
+          <t>1511894</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1594074</t>
+          <t>1594203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110581</t>
+          <t>110637</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>152188</t>
+          <t>155654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>183748</t>
+          <t>182902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>234695</t>
+          <t>234313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>305366</t>
+          <t>304121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>372734</t>
+          <t>373156</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>600538</t>
+          <t>597072</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642145</t>
+          <t>642089</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>543803</t>
+          <t>544185</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>594750</t>
+          <t>595596</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1158490</t>
+          <t>1158068</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1225858</t>
+          <t>1227103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,14%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145050</t>
+          <t>145627</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>192844</t>
+          <t>194914</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>246331</t>
+          <t>248156</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>310076</t>
+          <t>307551</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>408323</t>
+          <t>405809</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>482284</t>
+          <t>485351</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,64%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>739045</t>
+          <t>736975</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>786839</t>
+          <t>786262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>727515</t>
+          <t>730040</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>791260</t>
+          <t>789435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1487196</t>
+          <t>1484129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1561157</t>
+          <t>1563671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>584514</t>
+          <t>583392</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>670850</t>
+          <t>675663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>963266</t>
+          <t>959073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1073617</t>
+          <t>1071321</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1567702</t>
+          <t>1576319</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1716472</t>
+          <t>1720911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,97%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2698780</t>
+          <t>2693967</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2785116</t>
+          <t>2786238</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2448372</t>
+          <t>2450668</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2558723</t>
+          <t>2562916</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5175146</t>
+          <t>5170707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5323916</t>
+          <t>5315299</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>77,13%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2023</t>
+          <t>Población que el dolor dificultó su trabajo habitual las últimas 4 semanas en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>172814</t>
+          <t>172632</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>218650</t>
+          <t>218779</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>252553</t>
+          <t>251758</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>291085</t>
+          <t>292531</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>435068</t>
+          <t>435111</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>498744</t>
+          <t>497333</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,95%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>416060</t>
+          <t>415931</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>461896</t>
+          <t>462078</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>384667</t>
+          <t>383221</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423199</t>
+          <t>423994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>811719</t>
+          <t>813130</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>875395</t>
+          <t>875352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>125319</t>
+          <t>111206</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>298589</t>
+          <t>301407</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>336033</t>
+          <t>339013</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>386402</t>
+          <t>389383</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>403580</t>
+          <t>380962</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>686973</t>
+          <t>679389</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,64%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>891944</t>
+          <t>889126</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1065214</t>
+          <t>1079327</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>570228</t>
+          <t>567247</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>620597</t>
+          <t>617617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1460190</t>
+          <t>1467774</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1743583</t>
+          <t>1766201</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146740</t>
+          <t>144368</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>192914</t>
+          <t>191485</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>270390</t>
+          <t>267395</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>657662</t>
+          <t>711594</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>429353</t>
+          <t>430460</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>941312</t>
+          <t>921593</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>56,28%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>511766</t>
+          <t>513195</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>557940</t>
+          <t>560312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>275129</t>
+          <t>221197</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>662401</t>
+          <t>665396</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>696160</t>
+          <t>715879</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1208119</t>
+          <t>1207012</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,71%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>237825</t>
+          <t>239547</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>294390</t>
+          <t>296503</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>331455</t>
+          <t>330567</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>453129</t>
+          <t>453747</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>598701</t>
+          <t>600202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>726311</t>
+          <t>718733</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>632441</t>
+          <t>630328</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>689006</t>
+          <t>687284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639956</t>
+          <t>639338</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>761630</t>
+          <t>762518</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1293605</t>
+          <t>1301183</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1421215</t>
+          <t>1419714</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>676549</t>
+          <t>670918</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>949686</t>
+          <t>946553</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1309506</t>
+          <t>1314973</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1857299</t>
+          <t>1891058</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2109118</t>
+          <t>2109545</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2856413</t>
+          <t>2774079</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -8054,17 +8054,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2596949</t>
+          <t>2596950</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2507068</t>
+          <t>2510202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2780205</t>
+          <t>2785837</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1800960</t>
+          <t>1767201</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2348753</t>
+          <t>2343286</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4258600</t>
+          <t>4340934</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5005895</t>
+          <t>5005468</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,35%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3456754</t>
+          <t>3456755</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3456754</t>
+          <t>3456755</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3456754</t>
+          <t>3456755</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">

--- a/data/trans_orig/P11_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P11_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>133761</t>
+          <t>131854</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>175728</t>
+          <t>173328</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183979</t>
+          <t>182662</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>230559</t>
+          <t>229769</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>327909</t>
+          <t>327567</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>389946</t>
+          <t>393313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,45%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>518284</t>
+          <t>520684</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>560251</t>
+          <t>562158</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>75,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>457792</t>
+          <t>458582</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>504372</t>
+          <t>505689</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>992417</t>
+          <t>989050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1054454</t>
+          <t>1054796</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>129338</t>
+          <t>127971</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>174227</t>
+          <t>172409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>231559</t>
+          <t>226729</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>289166</t>
+          <t>284868</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>372426</t>
+          <t>373485</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>442801</t>
+          <t>445708</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,09%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>787573</t>
+          <t>789391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>832462</t>
+          <t>833829</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>679227</t>
+          <t>683525</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>736834</t>
+          <t>741664</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1487392</t>
+          <t>1484485</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1557767</t>
+          <t>1556708</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,65%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111039</t>
+          <t>111070</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155780</t>
+          <t>154479</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>215567</t>
+          <t>212208</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>266031</t>
+          <t>264614</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>337671</t>
+          <t>338273</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>403928</t>
+          <t>405337</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,75%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>522729</t>
+          <t>524030</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>567470</t>
+          <t>567439</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>417810</t>
+          <t>419227</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>468274</t>
+          <t>471633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>958422</t>
+          <t>957013</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1024679</t>
+          <t>1024077</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,17%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139991</t>
+          <t>138267</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>183880</t>
+          <t>183735</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>255020</t>
+          <t>255214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>315188</t>
+          <t>311843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>409749</t>
+          <t>406990</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>483545</t>
+          <t>479358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>758342</t>
+          <t>758487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>802231</t>
+          <t>803955</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>723424</t>
+          <t>726769</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>783592</t>
+          <t>783398</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1497289</t>
+          <t>1501476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1571085</t>
+          <t>1573844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>554337</t>
+          <t>553244</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>643076</t>
+          <t>639974</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>933971</t>
+          <t>938814</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1042379</t>
+          <t>1044684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1510899</t>
+          <t>1508456</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1649700</t>
+          <t>1648796</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,77%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2633467</t>
+          <t>2636569</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2722206</t>
+          <t>2723299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2336818</t>
+          <t>2334513</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2445226</t>
+          <t>2440383</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5006041</t>
+          <t>5006945</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5144842</t>
+          <t>5147285</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,34%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112136</t>
+          <t>111168</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154348</t>
+          <t>152232</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>210018</t>
+          <t>210371</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>265428</t>
+          <t>263394</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>336984</t>
+          <t>334841</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>403605</t>
+          <t>400648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>543468</t>
+          <t>545584</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>585680</t>
+          <t>586648</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>429748</t>
+          <t>431782</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>485158</t>
+          <t>484805</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>989387</t>
+          <t>992344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1056008</t>
+          <t>1058151</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>75,96%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>182833</t>
+          <t>182219</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>236595</t>
+          <t>237560</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>293664</t>
+          <t>292913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>355200</t>
+          <t>355587</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>496973</t>
+          <t>492299</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>576251</t>
+          <t>577599</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,26%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>776945</t>
+          <t>775980</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>830707</t>
+          <t>831321</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674993</t>
+          <t>674606</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>736529</t>
+          <t>737280</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,52%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1467482</t>
+          <t>1466134</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1546760</t>
+          <t>1551434</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>82894</t>
+          <t>81584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>122682</t>
+          <t>121623</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>195050</t>
+          <t>195944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>246672</t>
+          <t>245932</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>288273</t>
+          <t>286323</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>355284</t>
+          <t>352432</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>631831</t>
+          <t>632890</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>671619</t>
+          <t>672929</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>530502</t>
+          <t>531242</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582124</t>
+          <t>581230</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1176403</t>
+          <t>1179255</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1243414</t>
+          <t>1245364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,31%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>175568</t>
+          <t>178224</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>226891</t>
+          <t>231248</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>305167</t>
+          <t>303994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>364037</t>
+          <t>365219</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>494311</t>
+          <t>494865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>577310</t>
+          <t>572714</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,7%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>716927</t>
+          <t>712570</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>768250</t>
+          <t>765594</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>75,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>687864</t>
+          <t>686682</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>746734</t>
+          <t>747907</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1418409</t>
+          <t>1423005</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1501408</t>
+          <t>1500854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,2%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>597889</t>
+          <t>597213</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>692568</t>
+          <t>692784</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1059235</t>
+          <t>1054956</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1173836</t>
+          <t>1165572</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1681452</t>
+          <t>1686514</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1828983</t>
+          <t>1834573</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2717119</t>
+          <t>2716903</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2811798</t>
+          <t>2812474</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2380608</t>
+          <t>2388872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2495209</t>
+          <t>2499488</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5135148</t>
+          <t>5129558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5282679</t>
+          <t>5277617</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,78%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>116144</t>
+          <t>116435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>158020</t>
+          <t>158723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>190700</t>
+          <t>192999</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>241294</t>
+          <t>240923</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>322654</t>
+          <t>321272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>389120</t>
+          <t>387277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,01%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>511029</t>
+          <t>510326</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>552905</t>
+          <t>552614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424766</t>
+          <t>425137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>475360</t>
+          <t>473061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>945989</t>
+          <t>947832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1012455</t>
+          <t>1013837</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>75,94%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>168183</t>
+          <t>165290</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>215856</t>
+          <t>213194</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>285019</t>
+          <t>285970</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>347313</t>
+          <t>347541</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>461602</t>
+          <t>467982</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>543911</t>
+          <t>547342</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,62%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>800109</t>
+          <t>802771</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>847782</t>
+          <t>850675</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>692527</t>
+          <t>692299</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>754821</t>
+          <t>753870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1511894</t>
+          <t>1508463</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1594203</t>
+          <t>1587823</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110637</t>
+          <t>110235</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155654</t>
+          <t>154325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>182902</t>
+          <t>183921</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>234313</t>
+          <t>235133</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>304121</t>
+          <t>303634</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>373156</t>
+          <t>369962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,16%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>597072</t>
+          <t>598401</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>642089</t>
+          <t>642491</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>544185</t>
+          <t>543365</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>595596</t>
+          <t>594577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1158068</t>
+          <t>1161262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1227103</t>
+          <t>1227590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,17%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>145627</t>
+          <t>146239</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>194914</t>
+          <t>194295</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>248156</t>
+          <t>248748</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>307551</t>
+          <t>306001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>405809</t>
+          <t>406161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>485351</t>
+          <t>485246</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>736975</t>
+          <t>737594</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>786262</t>
+          <t>785650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>730040</t>
+          <t>731590</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>789435</t>
+          <t>788843</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,08%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1484129</t>
+          <t>1484234</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1563671</t>
+          <t>1563319</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>79,38%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>583392</t>
+          <t>585906</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>675663</t>
+          <t>673772</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>959073</t>
+          <t>957490</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1071321</t>
+          <t>1065099</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1576319</t>
+          <t>1570059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1720911</t>
+          <t>1711007</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,83%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2693967</t>
+          <t>2695858</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2786238</t>
+          <t>2783724</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2450668</t>
+          <t>2456890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2562916</t>
+          <t>2564499</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5170707</t>
+          <t>5180611</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5315299</t>
+          <t>5321559</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,13%</t>
+          <t>77,22%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>195904</t>
+          <t>211256</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>172632</t>
+          <t>188390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>218779</t>
+          <t>235350</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,47%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>271221</t>
+          <t>288516</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>251758</t>
+          <t>266579</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>292531</t>
+          <t>309084</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,14%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>467125</t>
+          <t>499772</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>435111</t>
+          <t>469506</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>497333</t>
+          <t>537168</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,75%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>438806</t>
+          <t>478449</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>415931</t>
+          <t>454355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>462078</t>
+          <t>501315</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>69,13%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,8%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>404531</t>
+          <t>444597</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>383221</t>
+          <t>424029</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>423994</t>
+          <t>466534</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,74%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>843338</t>
+          <t>923047</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>813130</t>
+          <t>885651</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>875352</t>
+          <t>953313</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,0%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634710</t>
+          <t>689705</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634710</t>
+          <t>689705</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634710</t>
+          <t>689705</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675752</t>
+          <t>733113</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310463</t>
+          <t>1422819</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310463</t>
+          <t>1422819</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310463</t>
+          <t>1422819</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>229403</t>
+          <t>250482</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111206</t>
+          <t>220284</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>301407</t>
+          <t>278333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>362999</t>
+          <t>398958</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>339013</t>
+          <t>370886</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>389383</t>
+          <t>425651</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>592402</t>
+          <t>649441</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>380962</t>
+          <t>607345</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>679389</t>
+          <t>690322</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>961130</t>
+          <t>795817</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>889126</t>
+          <t>767966</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1079327</t>
+          <t>826015</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,68%</t>
+          <t>73,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>593631</t>
+          <t>670242</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>567247</t>
+          <t>643549</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>617617</t>
+          <t>698314</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>65,31%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1554761</t>
+          <t>1466059</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1467774</t>
+          <t>1425178</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1766201</t>
+          <t>1508155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>67,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>71,29%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1190533</t>
+          <t>1046299</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1190533</t>
+          <t>1046299</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1190533</t>
+          <t>1046299</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956630</t>
+          <t>1069200</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956630</t>
+          <t>1069200</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956630</t>
+          <t>1069200</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2147163</t>
+          <t>2115500</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2147163</t>
+          <t>2115500</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2147163</t>
+          <t>2115500</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>168779</t>
+          <t>192867</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>144368</t>
+          <t>168589</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191485</t>
+          <t>221537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>422594</t>
+          <t>249082</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>267395</t>
+          <t>226235</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>711594</t>
+          <t>272649</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>591373</t>
+          <t>441949</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>430460</t>
+          <t>407521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>921593</t>
+          <t>476872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>535901</t>
+          <t>610206</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>513195</t>
+          <t>581536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>560312</t>
+          <t>634484</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>510197</t>
+          <t>562520</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>221197</t>
+          <t>538953</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>665396</t>
+          <t>585367</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1046099</t>
+          <t>1172726</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>715879</t>
+          <t>1137803</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1207012</t>
+          <t>1207154</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932791</t>
+          <t>811602</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932791</t>
+          <t>811602</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932791</t>
+          <t>811602</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1637472</t>
+          <t>1614675</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1637472</t>
+          <t>1614675</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1637472</t>
+          <t>1614675</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>265719</t>
+          <t>278707</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>239547</t>
+          <t>251293</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>296503</t>
+          <t>308327</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,99%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>413918</t>
+          <t>448537</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>330567</t>
+          <t>421074</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>453747</t>
+          <t>479693</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>679637</t>
+          <t>727244</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>600202</t>
+          <t>683660</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>718733</t>
+          <t>767906</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>661112</t>
+          <t>711355</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>630328</t>
+          <t>681735</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>687284</t>
+          <t>738769</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,01%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>679167</t>
+          <t>668341</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>639338</t>
+          <t>637185</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>762518</t>
+          <t>695804</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1340279</t>
+          <t>1379696</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1301183</t>
+          <t>1339034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1419714</t>
+          <t>1423280</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>67,55%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1093085</t>
+          <t>1116878</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1093085</t>
+          <t>1116878</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1093085</t>
+          <t>1116878</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019916</t>
+          <t>2106940</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019916</t>
+          <t>2106940</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019916</t>
+          <t>2106940</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>859805</t>
+          <t>933312</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>670918</t>
+          <t>875133</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>946553</t>
+          <t>985944</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1470732</t>
+          <t>1385094</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1314973</t>
+          <t>1331342</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1891058</t>
+          <t>1435380</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2330537</t>
+          <t>2318406</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2109545</t>
+          <t>2244434</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2774079</t>
+          <t>2401930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>33,08%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2596950</t>
+          <t>2595828</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2510202</t>
+          <t>2543196</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2785837</t>
+          <t>2654007</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2187527</t>
+          <t>2345700</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1767201</t>
+          <t>2295414</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2343286</t>
+          <t>2399452</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4784476</t>
+          <t>4941528</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4340934</t>
+          <t>4858004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5005468</t>
+          <t>5015500</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,08%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3456755</t>
+          <t>3529140</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3456755</t>
+          <t>3529140</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3456755</t>
+          <t>3529140</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658259</t>
+          <t>3730794</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658259</t>
+          <t>3730794</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658259</t>
+          <t>3730794</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7115013</t>
+          <t>7259934</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7115013</t>
+          <t>7259934</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7115013</t>
+          <t>7259934</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
